--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488144_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488144_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>J. TOMAIC TOMAIC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6665</v>
+        <v>6.3253</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5449</v>
+        <v>1.6685</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1217</v>
+        <v>4.6569</v>
       </c>
       <c r="G2" t="n">
-        <v>1.772</v>
+        <v>4.7503</v>
       </c>
       <c r="H2" t="n">
-        <v>1.127</v>
+        <v>1.5587</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6451</v>
+        <v>3.1917</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6778999999999999</v>
+        <v>3.6006</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5321</v>
+        <v>0.8622</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1458</v>
+        <v>2.7384</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0942</v>
+        <v>1.1498</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5949</v>
+        <v>0.6965</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4993</v>
+        <v>0.4533</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9646</v>
+        <v>4.0763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2089</v>
+        <v>-0.7781</v>
       </c>
       <c r="T2" t="n">
-        <v>0.776</v>
+        <v>-0.8378</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5671</v>
+        <v>0.0597</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8327</v>
+        <v>0.315</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2027</v>
+        <v>0.9439</v>
       </c>
       <c r="X2" t="n">
-        <v>0.63</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. TOMAIC TOMAIC</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.617</v>
+        <v>5.963</v>
       </c>
       <c r="E3" t="n">
-        <v>1.32</v>
+        <v>1.7182</v>
       </c>
       <c r="F3" t="n">
-        <v>5.297</v>
+        <v>4.2448</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7503</v>
+        <v>1.772</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5587</v>
+        <v>1.127</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1917</v>
+        <v>0.6451</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6006</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8622</v>
+        <v>0.5321</v>
       </c>
       <c r="L3" t="n">
-        <v>2.7384</v>
+        <v>0.1458</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1498</v>
+        <v>1.0942</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6965</v>
+        <v>0.5949</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4533</v>
+        <v>0.4993</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R3" t="n">
-        <v>4.0763</v>
+        <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4865</v>
+        <v>-0.4946</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1863</v>
+        <v>-0.0506</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6998</v>
+        <v>-0.444</v>
       </c>
       <c r="V3" t="n">
-        <v>0.315</v>
+        <v>2.8327</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9439</v>
+        <v>2.2027</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6289</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Á. CHAPARRO CARRASCO</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1324</v>
+        <v>3.415</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1324</v>
+        <v>0.3967</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3.0183</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1324</v>
+        <v>0.8341</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6441</v>
+        <v>0.0215</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4883</v>
+        <v>0.8126</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1324</v>
+        <v>0.2534</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6441</v>
+        <v>0.2013</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4883</v>
+        <v>0.0522</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.5806</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.1798</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.7604</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.7793</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.7793</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-1.1422</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.4856</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.6566</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>Á. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6004</v>
+        <v>3.1324</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2455</v>
+        <v>3.1324</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8459</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8341</v>
+        <v>3.1324</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0215</v>
+        <v>0.6441</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8126</v>
+        <v>2.4883</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2534</v>
+        <v>3.1324</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2013</v>
+        <v>0.6441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0522</v>
+        <v>2.4883</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5806</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1798</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7604</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9568</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1279</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.829</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4785</v>
+        <v>1.601</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.6355</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2119</v>
+        <v>2.2365</v>
       </c>
       <c r="G6" t="n">
         <v>1.8634</v>
@@ -922,13 +922,13 @@
         <v>2.594</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3119</v>
+        <v>-0.1893</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.4107</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1967</v>
+        <v>0.2213</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6289</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6949</v>
+        <v>1.2896</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3553</v>
+        <v>-3.0068</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0502</v>
+        <v>4.2964</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6238</v>
@@ -1000,13 +1000,13 @@
         <v>2.7793</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9053</v>
+        <v>-0.3106</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.475</v>
+        <v>-0.1265</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4303</v>
+        <v>-0.1841</v>
       </c>
       <c r="V7" t="n">
         <v>0.63</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0557</v>
+        <v>0.3853</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4802</v>
+        <v>-2.0885</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4246</v>
+        <v>2.4738</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5561</v>
@@ -1078,13 +1078,13 @@
         <v>2.4087</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9819</v>
+        <v>-0.5409</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8879</v>
+        <v>-0.4961</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.094</v>
+        <v>-0.0448</v>
       </c>
       <c r="V8" t="n">
         <v>1.2589</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2128</v>
+        <v>-0.7948</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.36</v>
+        <v>-0.8037</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1473</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2767</v>
+        <v>0.5682</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6116</v>
+        <v>-0.4579</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6652</v>
+        <v>1.0261</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3508</v>
+        <v>0.1908</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1849</v>
+        <v>-0.5972</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1659</v>
+        <v>0.788</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.3774</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4266</v>
+        <v>0.1393</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4993</v>
+        <v>0.2381</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6676</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0382</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7513</v>
+        <v>0.2664</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9949</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2435</v>
+        <v>0.3345</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5733</v>
+        <v>-1.2589</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5733</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1378</v>
+        <v>-1.04</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0975</v>
+        <v>-2.0888</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0403</v>
+        <v>1.0488</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5682</v>
+        <v>2.2767</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4579</v>
+        <v>1.6116</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0261</v>
+        <v>0.6652</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1908</v>
+        <v>1.3508</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5972</v>
+        <v>1.1849</v>
       </c>
       <c r="L10" t="n">
-        <v>0.788</v>
+        <v>0.1659</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3774</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1393</v>
+        <v>0.4266</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2381</v>
+        <v>0.4993</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3706</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.0382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0766</v>
+        <v>-0.0759</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3619</v>
+        <v>0.2661</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2853</v>
+        <v>-0.342</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2589</v>
+        <v>-1.5733</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2589</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1584</v>
+        <v>-1.3783</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7005</v>
+        <v>-1.9943</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5421</v>
+        <v>0.616</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9552</v>
@@ -1312,13 +1312,13 @@
         <v>0.1853</v>
       </c>
       <c r="S11" t="n">
-        <v>0.538</v>
+        <v>0.318</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4887</v>
+        <v>0.1949</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.625</v>
+        <v>18.8985</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.975099999999999</v>
+        <v>-3.701799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>22.6004</v>
+        <v>22.6005</v>
       </c>
       <c r="G12" t="n">
         <v>10.062</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2320999999999996</v>
+        <v>0.2320999999999994</v>
       </c>
       <c r="I12" t="n">
-        <v>9.8301</v>
+        <v>9.830100000000002</v>
       </c>
       <c r="J12" t="n">
         <v>4.081000000000001</v>
@@ -1381,7 +1381,7 @@
         <v>2.9193</v>
       </c>
       <c r="P12" t="n">
-        <v>9.2644</v>
+        <v>9.264399999999998</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.1172</v>
@@ -1390,10 +1390,10 @@
         <v>20.3816</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2208</v>
+        <v>-2.9472</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.287999999999999</v>
+        <v>-2.0144</v>
       </c>
       <c r="U12" t="n">
         <v>-0.9329000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2054</v>
+        <v>3.3074</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0892</v>
+        <v>2.1099</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1162</v>
+        <v>1.1975</v>
       </c>
       <c r="G13" t="n">
         <v>3.1642</v>
@@ -1468,13 +1468,13 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8076</v>
+        <v>0.9096</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3194</v>
+        <v>0.3401</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4882</v>
+        <v>0.5695</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3223</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCÍA</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6441</v>
+        <v>0.9373</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6441</v>
+        <v>0.7398</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.1976</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6441</v>
+        <v>-0.2373</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6441</v>
+        <v>-0.0377</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0.1996</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6441</v>
+        <v>0.4207</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6441</v>
+        <v>0.4207</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>-0.658</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.4584</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-0.1996</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0.0843</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.0134</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0.0709</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>S. VICENTE GARCÍA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1116</v>
+        <v>0.6441</v>
       </c>
       <c r="E15" t="n">
-        <v>0.446</v>
+        <v>0.6441</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3344</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2373</v>
+        <v>0.6441</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0377</v>
+        <v>0.6441</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1996</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4207</v>
+        <v>0.6441</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4207</v>
+        <v>0.6441</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.658</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4584</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1996</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.91</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3071</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6029</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7398</v>
+        <v>-1.2346</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7016</v>
+        <v>-1.3099</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0382</v>
+        <v>0.0752</v>
       </c>
       <c r="G17" t="n">
         <v>3.7082</v>
@@ -1780,13 +1780,13 @@
         <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2166</v>
+        <v>0.2885</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3656</v>
+        <v>0.0261</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1489</v>
+        <v>0.2624</v>
       </c>
       <c r="V17" t="n">
         <v>-2.2667</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.417</v>
+        <v>-2.8598</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.3625</v>
+        <v>-4.4604</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9455</v>
+        <v>1.6006</v>
       </c>
       <c r="G18" t="n">
         <v>-1.9187</v>
@@ -1858,13 +1858,13 @@
         <v>1.4823</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6762</v>
+        <v>-0.1191</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0373</v>
+        <v>-0.1352</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6389</v>
+        <v>0.0161</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0073</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FROUFE PEREZ</t>
+          <t>T. GARRETT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7451</v>
+        <v>-3.936</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.019</v>
+        <v>-5.524</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2739</v>
+        <v>1.588</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.9422</v>
+        <v>-2.4348</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1113</v>
+        <v>-1.9034</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.8309</v>
+        <v>-0.5313</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.9026</v>
+        <v>-2.9754</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.976</v>
+        <v>-2.4055</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9265</v>
+        <v>-0.5699</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0397</v>
+        <v>0.5406</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8648</v>
+        <v>0.502</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9044</v>
+        <v>0.0386</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.297</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q19" t="n">
         <v>-3.3352</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2426</v>
+        <v>0.7222</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.1576</v>
       </c>
       <c r="U19" t="n">
-        <v>2.3383</v>
+        <v>0.5645</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2516</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3144</v>
+        <v>0.6289</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0629</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. CATALDO</t>
+          <t>A. FROUFE PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0215</v>
+        <v>-4.5026</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8485</v>
+        <v>-6.7252</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1729</v>
+        <v>2.2226</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7855</v>
+        <v>-4.9422</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0283</v>
+        <v>-1.1113</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7572</v>
+        <v>-3.8309</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2517</v>
+        <v>-3.9026</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9152</v>
+        <v>-1.976</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6635</v>
+        <v>-1.9265</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5338</v>
+        <v>-1.0397</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1131</v>
+        <v>0.8648</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4207</v>
+        <v>-1.9044</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4087</v>
+        <v>-1.297</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7793</v>
+        <v>-3.3352</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3706</v>
+        <v>2.0382</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1172</v>
+        <v>1.4851</v>
       </c>
       <c r="T20" t="n">
-        <v>0.868</v>
+        <v>0.1981</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2492</v>
+        <v>1.287</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9444</v>
+        <v>0.2516</v>
       </c>
       <c r="W20" t="n">
         <v>0.3144</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2589</v>
+        <v>-0.0629</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. GARRETT</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9256</v>
+        <v>-4.6299</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.0137</v>
+        <v>-5.4526</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0881</v>
+        <v>0.8227</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4348</v>
+        <v>-5.9827</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9034</v>
+        <v>-3.0966</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5313</v>
+        <v>-2.8862</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.9754</v>
+        <v>-4.5891</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.4055</v>
+        <v>-3.999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5699</v>
+        <v>-0.59</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5406</v>
+        <v>-1.3937</v>
       </c>
       <c r="N21" t="n">
-        <v>0.502</v>
+        <v>0.9025</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0386</v>
+        <v>-2.2961</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2234</v>
+        <v>-1.297</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.3352</v>
+        <v>-2.4087</v>
       </c>
       <c r="R21" t="n">
         <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2674</v>
+        <v>1.076</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.332</v>
+        <v>0.2864</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0646</v>
+        <v>0.7896</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.5738</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6289</v>
+        <v>1.2589</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6289</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>B. CATALDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3423</v>
+        <v>-4.6503</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.7464</v>
+        <v>-2.534</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4041</v>
+        <v>-2.1162</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.9827</v>
+        <v>-1.7855</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0966</v>
+        <v>-1.0283</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8862</v>
+        <v>-0.7572</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.5891</v>
+        <v>-0.2517</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.999</v>
+        <v>-0.9152</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.59</v>
+        <v>0.6635</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3937</v>
+        <v>-1.5338</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9025</v>
+        <v>-0.1131</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.2961</v>
+        <v>-1.4207</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.297</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4087</v>
+        <v>-2.7793</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3636</v>
+        <v>0.4884</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0074</v>
+        <v>0.1825</v>
       </c>
       <c r="U22" t="n">
-        <v>0.371</v>
+        <v>0.3059</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5738</v>
+        <v>-0.9444</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X22" t="n">
-        <v>0.315</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="23">
@@ -2203,25 +2203,25 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.6252</v>
+        <v>-17.3194</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.6004</v>
+        <v>-22.6003</v>
       </c>
       <c r="F23" t="n">
-        <v>3.9753</v>
+        <v>5.281</v>
       </c>
       <c r="G23" t="n">
         <v>-10.0621</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2321999999999989</v>
+        <v>-0.2321999999999995</v>
       </c>
       <c r="I23" t="n">
         <v>-9.83</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.9812</v>
+        <v>-5.981199999999999</v>
       </c>
       <c r="K23" t="n">
         <v>-3.0616</v>
@@ -2230,7 +2230,7 @@
         <v>-2.9193</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.081200000000001</v>
+        <v>-4.0812</v>
       </c>
       <c r="N23" t="n">
         <v>2.8296</v>
@@ -2239,7 +2239,7 @@
         <v>-6.910500000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-9.264200000000001</v>
+        <v>-9.264199999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-20.3816</v>
@@ -2248,22 +2248,22 @@
         <v>11.1173</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2208</v>
+        <v>4.526400000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9329</v>
+        <v>0.9328</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2878</v>
+        <v>3.5935</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.519299999999999</v>
+        <v>-2.5193</v>
       </c>
       <c r="W23" t="n">
         <v>2.8294</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.3488</v>
+        <v>-5.348799999999999</v>
       </c>
     </row>
   </sheetData>
